--- a/sbce_config.xlsx
+++ b/sbce_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszokoly\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFED17C2-9494-41FF-B348-A9909413A92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAC8B52-D57E-4634-B243-640C9474AAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{B9974296-33B4-464A-B6B3-E66B7C96D59B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9974296-33B4-464A-B6B3-E66B7C96D59B}"/>
   </bookViews>
   <sheets>
     <sheet name="SBCEMS" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="148">
   <si>
     <t>datastore</t>
   </si>
@@ -342,9 +342,6 @@
     <t>M1 NIC Port-group / Bridge name</t>
   </si>
   <si>
-    <t>Time Zone - Time Zone in which device is located in GMT</t>
-  </si>
-  <si>
     <t>EMS+SBCE</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
     <t>CA</t>
   </si>
   <si>
-    <t>GMT-7</t>
-  </si>
-  <si>
     <t>10.10.48.250</t>
   </si>
   <si>
@@ -481,6 +475,15 @@
   </si>
   <si>
     <t>10.10.48.200</t>
+  </si>
+  <si>
+    <t>America/Edmonton</t>
+  </si>
+  <si>
+    <t>Time Zone - Time Zone in which device is located (for example America/Edmonton)</t>
+  </si>
+  <si>
+    <t>Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
 </sst>
 </file>
@@ -2597,7 +2600,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -2608,7 +2611,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -2619,7 +2622,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -2630,7 +2633,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -2641,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -2652,7 +2655,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -2663,7 +2666,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -2685,7 +2688,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -2696,7 +2699,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -2707,7 +2710,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -2740,7 +2743,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -2751,7 +2754,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -2762,7 +2765,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -2800,7 +2803,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -2823,7 +2826,7 @@
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
@@ -2834,7 +2837,7 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -2845,7 +2848,7 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
@@ -2856,7 +2859,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -2867,7 +2870,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
@@ -2878,10 +2881,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2889,7 +2892,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -2908,7 +2911,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -2979,7 +2982,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -2990,7 +2993,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -3001,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -3012,7 +3015,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -3023,7 +3026,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -3034,7 +3037,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -3072,7 +3075,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -3083,7 +3086,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -3094,10 +3097,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3105,10 +3108,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3227,7 +3230,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{392BA8B5-DFCE-4FAD-B98D-8723D09F28FD}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{EBC16548-B245-4CF4-939A-FDA1B969F099}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -3243,9 +3246,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{9E9590C0-45C5-4BD8-9C2E-FE8C612E3CFE}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{418585B9-E084-4EF8-90E7-B9429671DD54}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6617306C-E92F-4A25-8274-DA7845B13381}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -3293,7 +3293,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -3304,7 +3304,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -3315,7 +3315,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -3326,7 +3326,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -3348,7 +3348,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -3359,7 +3359,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -3381,7 +3381,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -3392,7 +3392,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -3403,7 +3403,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -3436,7 +3436,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -3447,7 +3447,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -3458,7 +3458,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -3496,7 +3496,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -3519,7 +3519,7 @@
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
@@ -3530,7 +3530,7 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -3541,7 +3541,7 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
@@ -3552,7 +3552,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -3563,7 +3563,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
@@ -3574,10 +3574,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -3585,7 +3585,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -3604,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -3675,7 +3675,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -3686,7 +3686,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -3769,7 +3769,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3777,7 +3777,7 @@
         <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3891,7 +3891,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{EF62750C-8857-4AB1-B612-1A1542DB1E87}">
       <formula1>8</formula1>
     </dataValidation>
@@ -3916,9 +3916,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{1C138210-67AE-438B-8CBB-8FA5DEEF6A8C}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{DEEFF223-EB8F-4787-A93F-E275895BF6B8}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{1B876CDA-B7A1-4E84-83F8-86024040D063}">
       <formula1>"primary,secondary"</formula1>
@@ -3956,7 +3953,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -3967,7 +3964,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -3978,7 +3975,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -3989,7 +3986,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -4000,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -4011,7 +4008,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -4022,7 +4019,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -4044,7 +4041,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -4055,7 +4052,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -4066,7 +4063,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -4099,7 +4096,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -4110,7 +4107,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -4121,7 +4118,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -4159,7 +4156,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -4218,10 +4215,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -4229,7 +4226,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -4248,7 +4245,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -4259,7 +4256,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -4322,7 +4319,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -4333,7 +4330,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -4344,7 +4341,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -4355,7 +4352,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -4366,7 +4363,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -4377,7 +4374,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -4388,7 +4385,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -4399,7 +4396,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -4421,7 +4418,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -4432,7 +4429,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -4443,10 +4440,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -4454,10 +4451,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -4571,7 +4568,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{67CA13E8-E016-4423-9E76-67C70E6F46AE}">
       <formula1>8</formula1>
     </dataValidation>
@@ -4596,9 +4593,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{6CCA4F8F-F58F-4A3A-8580-63A6C06FD65A}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{CAB7A839-1725-4A5D-BDB8-E977BA651B56}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{FC373F15-8828-49DF-BCDC-883EA220B5EB}">
       <formula1>"primary,secondary"</formula1>
@@ -4636,7 +4630,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -4647,7 +4641,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -4658,7 +4652,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -4669,7 +4663,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -4680,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -4691,7 +4685,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -4702,7 +4696,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -4724,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -4735,7 +4729,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -4746,7 +4740,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -4779,7 +4773,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -4790,7 +4784,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -4801,7 +4795,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -4839,7 +4833,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -4898,10 +4892,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -4909,7 +4903,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -4928,7 +4922,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -4939,7 +4933,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -5002,7 +4996,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -5013,7 +5007,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -5024,7 +5018,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -5035,7 +5029,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -5046,7 +5040,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -5057,7 +5051,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -5068,7 +5062,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -5079,7 +5073,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -5101,7 +5095,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -5112,7 +5106,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -5123,10 +5117,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -5134,10 +5128,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5251,7 +5245,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{9CDFC943-7388-48AF-AD1B-3E50DD0CF0E7}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{A8333A30-E8A9-468B-9448-D18959240DFC}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -5267,9 +5261,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{717F3864-B273-4E2C-B878-EF25CE118B6C}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{D0FC8359-F84F-456C-95CD-0C9BDD57E80C}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{E028E9F8-6DAB-4545-AAE2-710B220689B9}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -5316,7 +5307,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -5327,7 +5318,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -5338,7 +5329,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -5349,7 +5340,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -5360,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -5371,7 +5362,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -5382,7 +5373,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -5404,7 +5395,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -5415,7 +5406,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -5426,7 +5417,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -5459,7 +5450,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -5470,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -5481,7 +5472,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -5519,7 +5510,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -5542,7 +5533,7 @@
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
@@ -5553,7 +5544,7 @@
         <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -5564,7 +5555,7 @@
         <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
@@ -5575,7 +5566,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -5586,7 +5577,7 @@
         <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
@@ -5597,10 +5588,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -5608,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -5627,7 +5618,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -5698,7 +5689,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -5709,7 +5700,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -5792,7 +5783,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -5800,7 +5791,7 @@
         <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5914,7 +5905,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{203A9BDA-7863-4615-A22B-52374A439B24}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{2F8FB1CB-92F7-4ADC-A186-44E9FD59E1A4}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -5930,9 +5921,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{E0F141F2-4E1E-4356-8BA4-D6D05AA21F65}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{4BA2C49C-DF44-469B-AAFB-EE6BA426F76C}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{66805C94-14D3-445E-B9F4-354B83DE5AB6}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -5979,7 +5967,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -5990,7 +5978,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -6001,7 +5989,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -6012,7 +6000,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -6023,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -6034,7 +6022,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -6045,7 +6033,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -6067,7 +6055,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -6078,7 +6066,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -6089,7 +6077,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -6122,7 +6110,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -6133,7 +6121,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -6144,7 +6132,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -6182,7 +6170,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -6241,10 +6229,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -6252,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -6271,7 +6259,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -6282,7 +6270,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -6345,7 +6333,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -6356,7 +6344,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -6367,7 +6355,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -6378,7 +6366,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -6389,7 +6377,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -6400,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -6411,7 +6399,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -6422,7 +6410,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -6444,7 +6432,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -6455,7 +6443,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -6466,10 +6454,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -6477,10 +6465,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6594,7 +6582,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Host IP or FQDN" sqref="B3" xr:uid="{FA3A7B80-07D9-4825-A615-8BD925E9A05B}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{D8E0870F-3232-41F6-B6A1-0FEFB6F32BEC}">
       <formula1>"DUAL_STACK,IPV4"</formula1>
@@ -6610,9 +6598,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{6C6982DB-D9DE-4130-91B5-F3C69078F64E}">
       <formula1>"primary,secondary"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{4D7A7E39-B4CD-4684-BF9C-E747FC364C9C}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{7A665DB2-9C16-4CF0-8005-36158EA79B67}">
       <formula1>"A1,A2,B1,B2"</formula1>
@@ -6659,7 +6644,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -6670,7 +6655,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -6681,7 +6666,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -6692,7 +6677,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -6703,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -6714,7 +6699,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -6725,7 +6710,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -6747,7 +6732,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -6758,7 +6743,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -6769,7 +6754,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -6802,7 +6787,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -6813,7 +6798,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -6824,7 +6809,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -6862,7 +6847,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -6921,10 +6906,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -6932,7 +6917,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -6951,7 +6936,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -6962,7 +6947,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -7025,7 +7010,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -7036,7 +7021,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -7047,7 +7032,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -7058,7 +7043,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -7069,7 +7054,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -7080,7 +7065,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -7091,7 +7076,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -7102,7 +7087,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -7124,7 +7109,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -7135,7 +7120,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -7146,10 +7131,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -7157,10 +7142,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7274,7 +7259,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{5A5820D3-99F5-447E-9698-788C3515B4E8}">
       <formula1>8</formula1>
     </dataValidation>
@@ -7299,9 +7284,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{0A380C42-ECEE-49B9-8CD7-617B0442832E}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{85EF6794-38BD-4967-9600-2C767C5DE227}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{31802C4A-0599-49EF-A550-CFE48CD453EE}">
       <formula1>"primary,secondary"</formula1>
@@ -7339,7 +7321,7 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -7350,7 +7332,7 @@
         <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -7361,7 +7343,7 @@
         <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -7372,7 +7354,7 @@
         <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
         <v>92</v>
@@ -7383,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
@@ -7394,7 +7376,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
@@ -7405,7 +7387,7 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
@@ -7427,7 +7409,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -7438,7 +7420,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -7449,7 +7431,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -7482,7 +7464,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -7493,7 +7475,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -7504,7 +7486,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -7542,7 +7524,7 @@
         <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
@@ -7601,10 +7583,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -7612,7 +7594,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -7631,7 +7613,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -7642,7 +7624,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -7705,7 +7687,7 @@
         <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -7716,7 +7698,7 @@
         <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
         <v>98</v>
@@ -7727,7 +7709,7 @@
         <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>75</v>
@@ -7738,7 +7720,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>77</v>
@@ -7749,7 +7731,7 @@
         <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
         <v>79</v>
@@ -7760,7 +7742,7 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -7798,7 +7780,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
         <v>85</v>
@@ -7809,7 +7791,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -7820,10 +7802,10 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -7831,10 +7813,10 @@
         <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7948,7 +7930,7 @@
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation type="textLength" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B36" xr:uid="{67DFEABE-E9D9-492A-B08E-BC5D4A7DB198}">
       <formula1>8</formula1>
     </dataValidation>
@@ -7973,9 +7955,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45" xr:uid="{08AF66F3-57CB-4199-ABA0-AA25F929E71A}">
       <formula1>"A1,A2,B1,B2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B27" xr:uid="{08488717-1CD6-44C5-946D-7721D9E5AE65}">
-      <formula1>"GMT-3,GMT-4,GMT-5,GMT-5,GMT-6,GMT-7,GMT-8"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13" xr:uid="{D264AB75-6254-4A82-82FB-610BF04E4231}">
       <formula1>"primary,secondary"</formula1>
